--- a/Phylogenetic_analysis.xlsx
+++ b/Phylogenetic_analysis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stoces\Documents\Cesky_Hradek\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CC97717-A3D5-4368-8AE2-B67E88AA0CA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24DB9615-8839-4949-B7C5-53A8178B1FC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2628" yWindow="864" windowWidth="21600" windowHeight="12588" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="251">
   <si>
     <t>Abax_parp</t>
   </si>
@@ -793,6 +793,9 @@
   <si>
     <t>Trichotichnus laevicollis (Duftschmid, 1812)</t>
   </si>
+  <si>
+    <t>ID</t>
+  </si>
 </sst>
 </file>
 
@@ -83263,13 +83266,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B8B9021-7AA4-4E14-A5C1-A19342DAA36A}">
-  <dimension ref="A1:G306"/>
+  <dimension ref="A1:H306"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="6" max="6" width="12.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>87</v>
       </c>
@@ -83291,8 +83294,11 @@
       <c r="G1" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H1" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>2003</v>
       </c>
@@ -83314,8 +83320,11 @@
       <c r="G2">
         <v>600</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2003</v>
       </c>
@@ -83337,8 +83346,11 @@
       <c r="G3">
         <v>520</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2003</v>
       </c>
@@ -83360,8 +83372,11 @@
       <c r="G4">
         <v>520</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2003</v>
       </c>
@@ -83383,8 +83398,11 @@
       <c r="G5">
         <v>790</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>2003</v>
       </c>
@@ -83406,8 +83424,11 @@
       <c r="G6">
         <v>790</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>2003</v>
       </c>
@@ -83429,8 +83450,11 @@
       <c r="G7">
         <v>810</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>2003</v>
       </c>
@@ -83452,8 +83476,11 @@
       <c r="G8">
         <v>820</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2003</v>
       </c>
@@ -83475,8 +83502,11 @@
       <c r="G9">
         <v>800</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>2003</v>
       </c>
@@ -83498,8 +83528,11 @@
       <c r="G10">
         <v>700</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H10">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>2003</v>
       </c>
@@ -83521,8 +83554,11 @@
       <c r="G11">
         <v>760</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>2003</v>
       </c>
@@ -83544,8 +83580,11 @@
       <c r="G12">
         <v>800</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>2003</v>
       </c>
@@ -83567,8 +83606,11 @@
       <c r="G13">
         <v>580</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>2003</v>
       </c>
@@ -83590,8 +83632,11 @@
       <c r="G14">
         <v>520</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H14">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>2003</v>
       </c>
@@ -83613,8 +83658,11 @@
       <c r="G15">
         <v>680</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H15">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>2003</v>
       </c>
@@ -83636,8 +83684,11 @@
       <c r="G16">
         <v>700</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H16">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>2003</v>
       </c>
@@ -83659,8 +83710,11 @@
       <c r="G17">
         <v>800</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H17">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>2003</v>
       </c>
@@ -83682,8 +83736,11 @@
       <c r="G18">
         <v>740</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H18">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>2003</v>
       </c>
@@ -83705,8 +83762,11 @@
       <c r="G19">
         <v>770</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H19">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>2003</v>
       </c>
@@ -83728,8 +83788,11 @@
       <c r="G20">
         <v>600</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H20">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>2003</v>
       </c>
@@ -83751,8 +83814,11 @@
       <c r="G21">
         <v>520</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H21">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>2003</v>
       </c>
@@ -83774,8 +83840,11 @@
       <c r="G22">
         <v>520</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H22">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>2003</v>
       </c>
@@ -83797,8 +83866,11 @@
       <c r="G23">
         <v>790</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H23">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>2003</v>
       </c>
@@ -83820,8 +83892,11 @@
       <c r="G24">
         <v>790</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H24">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>2003</v>
       </c>
@@ -83843,8 +83918,11 @@
       <c r="G25">
         <v>810</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>2003</v>
       </c>
@@ -83866,8 +83944,11 @@
       <c r="G26">
         <v>820</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H26">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>2003</v>
       </c>
@@ -83889,8 +83970,11 @@
       <c r="G27">
         <v>800</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H27">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>2003</v>
       </c>
@@ -83912,8 +83996,11 @@
       <c r="G28">
         <v>700</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H28">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>2003</v>
       </c>
@@ -83935,8 +84022,11 @@
       <c r="G29">
         <v>760</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H29">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>2003</v>
       </c>
@@ -83958,8 +84048,11 @@
       <c r="G30">
         <v>800</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H30">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>2003</v>
       </c>
@@ -83981,8 +84074,11 @@
       <c r="G31">
         <v>580</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H31">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>2003</v>
       </c>
@@ -84004,8 +84100,11 @@
       <c r="G32">
         <v>520</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H32">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>2003</v>
       </c>
@@ -84027,8 +84126,11 @@
       <c r="G33">
         <v>680</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H33">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>2003</v>
       </c>
@@ -84050,8 +84152,11 @@
       <c r="G34">
         <v>700</v>
       </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H34">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>2003</v>
       </c>
@@ -84073,8 +84178,11 @@
       <c r="G35">
         <v>800</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H35">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>2003</v>
       </c>
@@ -84096,8 +84204,11 @@
       <c r="G36">
         <v>740</v>
       </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H36">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>2003</v>
       </c>
@@ -84119,8 +84230,11 @@
       <c r="G37">
         <v>770</v>
       </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H37">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>2003</v>
       </c>
@@ -84142,8 +84256,11 @@
       <c r="G38">
         <v>600</v>
       </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H38">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>2003</v>
       </c>
@@ -84165,8 +84282,11 @@
       <c r="G39">
         <v>520</v>
       </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H39">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>2003</v>
       </c>
@@ -84188,8 +84308,11 @@
       <c r="G40">
         <v>520</v>
       </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H40">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>2003</v>
       </c>
@@ -84211,8 +84334,11 @@
       <c r="G41">
         <v>790</v>
       </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H41">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>2003</v>
       </c>
@@ -84234,8 +84360,11 @@
       <c r="G42">
         <v>790</v>
       </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H42">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>2003</v>
       </c>
@@ -84257,8 +84386,11 @@
       <c r="G43">
         <v>810</v>
       </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H43">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>2003</v>
       </c>
@@ -84280,8 +84412,11 @@
       <c r="G44">
         <v>820</v>
       </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H44">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>2003</v>
       </c>
@@ -84303,8 +84438,11 @@
       <c r="G45">
         <v>800</v>
       </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H45">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>2003</v>
       </c>
@@ -84326,8 +84464,11 @@
       <c r="G46">
         <v>700</v>
       </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H46">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>2003</v>
       </c>
@@ -84349,8 +84490,11 @@
       <c r="G47">
         <v>760</v>
       </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H47">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>2003</v>
       </c>
@@ -84372,8 +84516,11 @@
       <c r="G48">
         <v>800</v>
       </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H48">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>2003</v>
       </c>
@@ -84395,8 +84542,11 @@
       <c r="G49">
         <v>580</v>
       </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H49">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>2003</v>
       </c>
@@ -84418,8 +84568,11 @@
       <c r="G50">
         <v>520</v>
       </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H50">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>2003</v>
       </c>
@@ -84441,8 +84594,11 @@
       <c r="G51">
         <v>680</v>
       </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H51">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>2003</v>
       </c>
@@ -84464,8 +84620,11 @@
       <c r="G52">
         <v>700</v>
       </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H52">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>2003</v>
       </c>
@@ -84487,8 +84646,11 @@
       <c r="G53">
         <v>800</v>
       </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H53">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>2003</v>
       </c>
@@ -84510,8 +84672,11 @@
       <c r="G54">
         <v>740</v>
       </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H54">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>2003</v>
       </c>
@@ -84533,8 +84698,11 @@
       <c r="G55">
         <v>770</v>
       </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H55">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>2003</v>
       </c>
@@ -84556,8 +84724,11 @@
       <c r="G56">
         <v>600</v>
       </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H56">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>2003</v>
       </c>
@@ -84579,8 +84750,11 @@
       <c r="G57">
         <v>520</v>
       </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H57">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>2003</v>
       </c>
@@ -84602,8 +84776,11 @@
       <c r="G58">
         <v>520</v>
       </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H58">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>2003</v>
       </c>
@@ -84625,8 +84802,11 @@
       <c r="G59">
         <v>790</v>
       </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H59">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>2003</v>
       </c>
@@ -84648,8 +84828,11 @@
       <c r="G60">
         <v>790</v>
       </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H60">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>2003</v>
       </c>
@@ -84671,8 +84854,11 @@
       <c r="G61">
         <v>810</v>
       </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H61">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>2003</v>
       </c>
@@ -84694,8 +84880,11 @@
       <c r="G62">
         <v>820</v>
       </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H62">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>2003</v>
       </c>
@@ -84717,8 +84906,11 @@
       <c r="G63">
         <v>800</v>
       </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H63">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>2003</v>
       </c>
@@ -84740,8 +84932,11 @@
       <c r="G64">
         <v>700</v>
       </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H64">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>2003</v>
       </c>
@@ -84763,8 +84958,11 @@
       <c r="G65">
         <v>760</v>
       </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H65">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>2003</v>
       </c>
@@ -84786,8 +84984,11 @@
       <c r="G66">
         <v>800</v>
       </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H66">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>2003</v>
       </c>
@@ -84809,8 +85010,11 @@
       <c r="G67">
         <v>580</v>
       </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H67">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>2003</v>
       </c>
@@ -84832,8 +85036,11 @@
       <c r="G68">
         <v>520</v>
       </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H68">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>2003</v>
       </c>
@@ -84855,8 +85062,11 @@
       <c r="G69">
         <v>680</v>
       </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H69">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>2003</v>
       </c>
@@ -84878,8 +85088,11 @@
       <c r="G70">
         <v>700</v>
       </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H70">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>2003</v>
       </c>
@@ -84901,8 +85114,11 @@
       <c r="G71">
         <v>800</v>
       </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H71">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>2003</v>
       </c>
@@ -84924,8 +85140,11 @@
       <c r="G72">
         <v>740</v>
       </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H72">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>2003</v>
       </c>
@@ -84947,8 +85166,11 @@
       <c r="G73">
         <v>770</v>
       </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H73">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>2004</v>
       </c>
@@ -84970,8 +85192,11 @@
       <c r="G74">
         <v>600</v>
       </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H74">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>2004</v>
       </c>
@@ -84993,8 +85218,11 @@
       <c r="G75">
         <v>520</v>
       </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H75">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>2004</v>
       </c>
@@ -85016,8 +85244,11 @@
       <c r="G76">
         <v>520</v>
       </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H76">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>2004</v>
       </c>
@@ -85039,8 +85270,11 @@
       <c r="G77">
         <v>790</v>
       </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H77">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>2004</v>
       </c>
@@ -85062,8 +85296,11 @@
       <c r="G78">
         <v>790</v>
       </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H78">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>2004</v>
       </c>
@@ -85085,8 +85322,11 @@
       <c r="G79">
         <v>810</v>
       </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H79">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>2004</v>
       </c>
@@ -85108,8 +85348,11 @@
       <c r="G80">
         <v>820</v>
       </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H80">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>2004</v>
       </c>
@@ -85131,8 +85374,11 @@
       <c r="G81">
         <v>800</v>
       </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H81">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>2004</v>
       </c>
@@ -85154,8 +85400,11 @@
       <c r="G82">
         <v>700</v>
       </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H82">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>2004</v>
       </c>
@@ -85177,8 +85426,11 @@
       <c r="G83">
         <v>760</v>
       </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H83">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>2004</v>
       </c>
@@ -85200,8 +85452,11 @@
       <c r="G84">
         <v>800</v>
       </c>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H84">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>2004</v>
       </c>
@@ -85223,8 +85478,11 @@
       <c r="G85">
         <v>580</v>
       </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H85">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>2004</v>
       </c>
@@ -85246,8 +85504,11 @@
       <c r="G86">
         <v>520</v>
       </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H86">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>2004</v>
       </c>
@@ -85269,8 +85530,11 @@
       <c r="G87">
         <v>680</v>
       </c>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H87">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>2004</v>
       </c>
@@ -85292,8 +85556,11 @@
       <c r="G88">
         <v>700</v>
       </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H88">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>2004</v>
       </c>
@@ -85315,8 +85582,11 @@
       <c r="G89">
         <v>800</v>
       </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H89">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>2004</v>
       </c>
@@ -85338,8 +85608,11 @@
       <c r="G90">
         <v>740</v>
       </c>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H90">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>2004</v>
       </c>
@@ -85361,8 +85634,11 @@
       <c r="G91">
         <v>770</v>
       </c>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H91">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>2004</v>
       </c>
@@ -85384,8 +85660,11 @@
       <c r="G92">
         <v>390</v>
       </c>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H92">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>2004</v>
       </c>
@@ -85407,8 +85686,11 @@
       <c r="G93">
         <v>480</v>
       </c>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H93">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>2004</v>
       </c>
@@ -85430,8 +85712,11 @@
       <c r="G94">
         <v>600</v>
       </c>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H94">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>2004</v>
       </c>
@@ -85453,8 +85738,11 @@
       <c r="G95">
         <v>520</v>
       </c>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H95">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>2004</v>
       </c>
@@ -85476,8 +85764,11 @@
       <c r="G96">
         <v>520</v>
       </c>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H96">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>2004</v>
       </c>
@@ -85499,8 +85790,11 @@
       <c r="G97">
         <v>790</v>
       </c>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H97">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>2004</v>
       </c>
@@ -85522,8 +85816,11 @@
       <c r="G98">
         <v>790</v>
       </c>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H98">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>2004</v>
       </c>
@@ -85545,8 +85842,11 @@
       <c r="G99">
         <v>810</v>
       </c>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H99">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>2004</v>
       </c>
@@ -85568,8 +85868,11 @@
       <c r="G100">
         <v>820</v>
       </c>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H100">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>2004</v>
       </c>
@@ -85591,8 +85894,11 @@
       <c r="G101">
         <v>800</v>
       </c>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H101">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>2004</v>
       </c>
@@ -85614,8 +85920,11 @@
       <c r="G102">
         <v>700</v>
       </c>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H102">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>2004</v>
       </c>
@@ -85637,8 +85946,11 @@
       <c r="G103">
         <v>760</v>
       </c>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H103">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>2004</v>
       </c>
@@ -85660,8 +85972,11 @@
       <c r="G104">
         <v>800</v>
       </c>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H104">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>2004</v>
       </c>
@@ -85683,8 +85998,11 @@
       <c r="G105">
         <v>580</v>
       </c>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H105">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>2004</v>
       </c>
@@ -85706,8 +86024,11 @@
       <c r="G106">
         <v>520</v>
       </c>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H106">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>2004</v>
       </c>
@@ -85729,8 +86050,11 @@
       <c r="G107">
         <v>680</v>
       </c>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H107">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>2004</v>
       </c>
@@ -85752,8 +86076,11 @@
       <c r="G108">
         <v>700</v>
       </c>
-    </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H108">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>2004</v>
       </c>
@@ -85775,8 +86102,11 @@
       <c r="G109">
         <v>800</v>
       </c>
-    </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H109">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>2004</v>
       </c>
@@ -85798,8 +86128,11 @@
       <c r="G110">
         <v>740</v>
       </c>
-    </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H110">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>2004</v>
       </c>
@@ -85821,8 +86154,11 @@
       <c r="G111">
         <v>770</v>
       </c>
-    </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H111">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>2004</v>
       </c>
@@ -85844,8 +86180,11 @@
       <c r="G112">
         <v>390</v>
       </c>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H112">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>2004</v>
       </c>
@@ -85867,8 +86206,11 @@
       <c r="G113">
         <v>480</v>
       </c>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H113">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>2004</v>
       </c>
@@ -85890,8 +86232,11 @@
       <c r="G114">
         <v>600</v>
       </c>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H114">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>2004</v>
       </c>
@@ -85913,8 +86258,11 @@
       <c r="G115">
         <v>520</v>
       </c>
-    </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H115">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>2004</v>
       </c>
@@ -85936,8 +86284,11 @@
       <c r="G116">
         <v>520</v>
       </c>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H116">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>2004</v>
       </c>
@@ -85959,8 +86310,11 @@
       <c r="G117">
         <v>790</v>
       </c>
-    </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H117">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>2004</v>
       </c>
@@ -85982,8 +86336,11 @@
       <c r="G118">
         <v>790</v>
       </c>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H118">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>2004</v>
       </c>
@@ -86005,8 +86362,11 @@
       <c r="G119">
         <v>810</v>
       </c>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H119">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>2004</v>
       </c>
@@ -86028,8 +86388,11 @@
       <c r="G120">
         <v>820</v>
       </c>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H120">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>2004</v>
       </c>
@@ -86051,8 +86414,11 @@
       <c r="G121">
         <v>800</v>
       </c>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H121">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>2004</v>
       </c>
@@ -86074,8 +86440,11 @@
       <c r="G122">
         <v>700</v>
       </c>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H122">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>2004</v>
       </c>
@@ -86097,8 +86466,11 @@
       <c r="G123">
         <v>760</v>
       </c>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H123">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>2004</v>
       </c>
@@ -86120,8 +86492,11 @@
       <c r="G124">
         <v>800</v>
       </c>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H124">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>2004</v>
       </c>
@@ -86143,8 +86518,11 @@
       <c r="G125">
         <v>580</v>
       </c>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H125">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>2004</v>
       </c>
@@ -86166,8 +86544,11 @@
       <c r="G126">
         <v>520</v>
       </c>
-    </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H126">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>2004</v>
       </c>
@@ -86189,8 +86570,11 @@
       <c r="G127">
         <v>680</v>
       </c>
-    </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H127">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>2004</v>
       </c>
@@ -86212,8 +86596,11 @@
       <c r="G128">
         <v>700</v>
       </c>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H128">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A129">
         <v>2004</v>
       </c>
@@ -86235,8 +86622,11 @@
       <c r="G129">
         <v>800</v>
       </c>
-    </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H129">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>2004</v>
       </c>
@@ -86258,8 +86648,11 @@
       <c r="G130">
         <v>740</v>
       </c>
-    </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H130">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A131">
         <v>2004</v>
       </c>
@@ -86281,8 +86674,11 @@
       <c r="G131">
         <v>770</v>
       </c>
-    </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H131">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>2004</v>
       </c>
@@ -86304,8 +86700,11 @@
       <c r="G132">
         <v>390</v>
       </c>
-    </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H132">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>2004</v>
       </c>
@@ -86327,8 +86726,11 @@
       <c r="G133">
         <v>480</v>
       </c>
-    </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H133">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>2004</v>
       </c>
@@ -86350,8 +86752,11 @@
       <c r="G134">
         <v>600</v>
       </c>
-    </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H134">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>2004</v>
       </c>
@@ -86373,8 +86778,11 @@
       <c r="G135">
         <v>520</v>
       </c>
-    </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H135">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>2004</v>
       </c>
@@ -86396,8 +86804,11 @@
       <c r="G136">
         <v>520</v>
       </c>
-    </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H136">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A137">
         <v>2004</v>
       </c>
@@ -86419,8 +86830,11 @@
       <c r="G137">
         <v>790</v>
       </c>
-    </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H137">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>2004</v>
       </c>
@@ -86442,8 +86856,11 @@
       <c r="G138">
         <v>790</v>
       </c>
-    </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H138">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>2004</v>
       </c>
@@ -86465,8 +86882,11 @@
       <c r="G139">
         <v>810</v>
       </c>
-    </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H139">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>2004</v>
       </c>
@@ -86488,8 +86908,11 @@
       <c r="G140">
         <v>820</v>
       </c>
-    </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H140">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A141">
         <v>2004</v>
       </c>
@@ -86511,8 +86934,11 @@
       <c r="G141">
         <v>800</v>
       </c>
-    </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H141">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A142">
         <v>2004</v>
       </c>
@@ -86534,8 +86960,11 @@
       <c r="G142">
         <v>700</v>
       </c>
-    </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H142">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A143">
         <v>2004</v>
       </c>
@@ -86557,8 +86986,11 @@
       <c r="G143">
         <v>760</v>
       </c>
-    </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H143">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A144">
         <v>2004</v>
       </c>
@@ -86580,8 +87012,11 @@
       <c r="G144">
         <v>800</v>
       </c>
-    </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H144">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A145">
         <v>2004</v>
       </c>
@@ -86603,8 +87038,11 @@
       <c r="G145">
         <v>580</v>
       </c>
-    </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H145">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>2004</v>
       </c>
@@ -86626,8 +87064,11 @@
       <c r="G146">
         <v>520</v>
       </c>
-    </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H146">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A147">
         <v>2004</v>
       </c>
@@ -86649,8 +87090,11 @@
       <c r="G147">
         <v>680</v>
       </c>
-    </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H147">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>2004</v>
       </c>
@@ -86672,8 +87116,11 @@
       <c r="G148">
         <v>700</v>
       </c>
-    </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H148">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>2004</v>
       </c>
@@ -86695,8 +87142,11 @@
       <c r="G149">
         <v>800</v>
       </c>
-    </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H149">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>2004</v>
       </c>
@@ -86718,8 +87168,11 @@
       <c r="G150">
         <v>740</v>
       </c>
-    </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H150">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A151">
         <v>2004</v>
       </c>
@@ -86741,8 +87194,11 @@
       <c r="G151">
         <v>770</v>
       </c>
-    </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H151">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>2004</v>
       </c>
@@ -86764,8 +87220,11 @@
       <c r="G152">
         <v>390</v>
       </c>
-    </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H152">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A153">
         <v>2004</v>
       </c>
@@ -86787,8 +87246,11 @@
       <c r="G153">
         <v>480</v>
       </c>
-    </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H153">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A154">
         <v>2005</v>
       </c>
@@ -86810,8 +87272,11 @@
       <c r="G154">
         <v>600</v>
       </c>
-    </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H154">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A155">
         <v>2005</v>
       </c>
@@ -86833,8 +87298,11 @@
       <c r="G155">
         <v>520</v>
       </c>
-    </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H155">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A156">
         <v>2005</v>
       </c>
@@ -86856,8 +87324,11 @@
       <c r="G156">
         <v>520</v>
       </c>
-    </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H156">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A157">
         <v>2005</v>
       </c>
@@ -86879,8 +87350,11 @@
       <c r="G157">
         <v>790</v>
       </c>
-    </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H157">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A158">
         <v>2005</v>
       </c>
@@ -86902,8 +87376,11 @@
       <c r="G158">
         <v>790</v>
       </c>
-    </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H158">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A159">
         <v>2005</v>
       </c>
@@ -86925,8 +87402,11 @@
       <c r="G159">
         <v>810</v>
       </c>
-    </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H159">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A160">
         <v>2005</v>
       </c>
@@ -86948,8 +87428,11 @@
       <c r="G160">
         <v>820</v>
       </c>
-    </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H160">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A161">
         <v>2005</v>
       </c>
@@ -86971,8 +87454,11 @@
       <c r="G161">
         <v>800</v>
       </c>
-    </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H161">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A162">
         <v>2005</v>
       </c>
@@ -86994,8 +87480,11 @@
       <c r="G162">
         <v>700</v>
       </c>
-    </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H162">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A163">
         <v>2005</v>
       </c>
@@ -87017,8 +87506,11 @@
       <c r="G163">
         <v>760</v>
       </c>
-    </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H163">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A164">
         <v>2005</v>
       </c>
@@ -87040,8 +87532,11 @@
       <c r="G164">
         <v>800</v>
       </c>
-    </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H164">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A165">
         <v>2005</v>
       </c>
@@ -87063,8 +87558,11 @@
       <c r="G165">
         <v>580</v>
       </c>
-    </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H165">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A166">
         <v>2005</v>
       </c>
@@ -87086,8 +87584,11 @@
       <c r="G166">
         <v>520</v>
       </c>
-    </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H166">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A167">
         <v>2005</v>
       </c>
@@ -87109,8 +87610,11 @@
       <c r="G167">
         <v>680</v>
       </c>
-    </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H167">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A168">
         <v>2005</v>
       </c>
@@ -87132,8 +87636,11 @@
       <c r="G168">
         <v>700</v>
       </c>
-    </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H168">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A169">
         <v>2005</v>
       </c>
@@ -87155,8 +87662,11 @@
       <c r="G169">
         <v>800</v>
       </c>
-    </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H169">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A170">
         <v>2005</v>
       </c>
@@ -87178,8 +87688,11 @@
       <c r="G170">
         <v>740</v>
       </c>
-    </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H170">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A171">
         <v>2005</v>
       </c>
@@ -87201,8 +87714,11 @@
       <c r="G171">
         <v>770</v>
       </c>
-    </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H171">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A172">
         <v>2005</v>
       </c>
@@ -87224,8 +87740,11 @@
       <c r="G172">
         <v>390</v>
       </c>
-    </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H172">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A173">
         <v>2005</v>
       </c>
@@ -87247,8 +87766,11 @@
       <c r="G173">
         <v>480</v>
       </c>
-    </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H173">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A174">
         <v>2005</v>
       </c>
@@ -87270,8 +87792,11 @@
       <c r="G174">
         <v>600</v>
       </c>
-    </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H174">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A175">
         <v>2005</v>
       </c>
@@ -87293,8 +87818,11 @@
       <c r="G175">
         <v>520</v>
       </c>
-    </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H175">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A176">
         <v>2005</v>
       </c>
@@ -87316,8 +87844,11 @@
       <c r="G176">
         <v>520</v>
       </c>
-    </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H176">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="177" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A177">
         <v>2005</v>
       </c>
@@ -87339,8 +87870,11 @@
       <c r="G177">
         <v>790</v>
       </c>
-    </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H177">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A178">
         <v>2005</v>
       </c>
@@ -87362,8 +87896,11 @@
       <c r="G178">
         <v>790</v>
       </c>
-    </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H178">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A179">
         <v>2005</v>
       </c>
@@ -87385,8 +87922,11 @@
       <c r="G179">
         <v>810</v>
       </c>
-    </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H179">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="180" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A180">
         <v>2005</v>
       </c>
@@ -87408,8 +87948,11 @@
       <c r="G180">
         <v>820</v>
       </c>
-    </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H180">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A181">
         <v>2005</v>
       </c>
@@ -87431,8 +87974,11 @@
       <c r="G181">
         <v>800</v>
       </c>
-    </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H181">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="182" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A182">
         <v>2005</v>
       </c>
@@ -87454,8 +88000,11 @@
       <c r="G182">
         <v>700</v>
       </c>
-    </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H182">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="183" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A183">
         <v>2005</v>
       </c>
@@ -87477,8 +88026,11 @@
       <c r="G183">
         <v>760</v>
       </c>
-    </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H183">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="184" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A184">
         <v>2005</v>
       </c>
@@ -87500,8 +88052,11 @@
       <c r="G184">
         <v>800</v>
       </c>
-    </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H184">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="185" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A185">
         <v>2005</v>
       </c>
@@ -87523,8 +88078,11 @@
       <c r="G185">
         <v>580</v>
       </c>
-    </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H185">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A186">
         <v>2005</v>
       </c>
@@ -87546,8 +88104,11 @@
       <c r="G186">
         <v>520</v>
       </c>
-    </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H186">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A187">
         <v>2005</v>
       </c>
@@ -87569,8 +88130,11 @@
       <c r="G187">
         <v>680</v>
       </c>
-    </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H187">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="188" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A188">
         <v>2005</v>
       </c>
@@ -87592,8 +88156,11 @@
       <c r="G188">
         <v>700</v>
       </c>
-    </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H188">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="189" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A189">
         <v>2005</v>
       </c>
@@ -87615,8 +88182,11 @@
       <c r="G189">
         <v>800</v>
       </c>
-    </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H189">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="190" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A190">
         <v>2005</v>
       </c>
@@ -87638,8 +88208,11 @@
       <c r="G190">
         <v>740</v>
       </c>
-    </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H190">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="191" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A191">
         <v>2005</v>
       </c>
@@ -87661,8 +88234,11 @@
       <c r="G191">
         <v>770</v>
       </c>
-    </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H191">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="192" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A192">
         <v>2005</v>
       </c>
@@ -87684,8 +88260,11 @@
       <c r="G192">
         <v>390</v>
       </c>
-    </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H192">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="193" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A193">
         <v>2005</v>
       </c>
@@ -87707,8 +88286,11 @@
       <c r="G193">
         <v>480</v>
       </c>
-    </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H193">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="194" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A194">
         <v>2005</v>
       </c>
@@ -87730,8 +88312,11 @@
       <c r="G194">
         <v>600</v>
       </c>
-    </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H194">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A195">
         <v>2005</v>
       </c>
@@ -87753,8 +88338,11 @@
       <c r="G195">
         <v>520</v>
       </c>
-    </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H195">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A196">
         <v>2005</v>
       </c>
@@ -87776,8 +88364,11 @@
       <c r="G196">
         <v>520</v>
       </c>
-    </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H196">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A197">
         <v>2005</v>
       </c>
@@ -87799,8 +88390,11 @@
       <c r="G197">
         <v>790</v>
       </c>
-    </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H197">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A198">
         <v>2005</v>
       </c>
@@ -87822,8 +88416,11 @@
       <c r="G198">
         <v>790</v>
       </c>
-    </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H198">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="199" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A199">
         <v>2005</v>
       </c>
@@ -87845,8 +88442,11 @@
       <c r="G199">
         <v>810</v>
       </c>
-    </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H199">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="200" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A200">
         <v>2005</v>
       </c>
@@ -87868,8 +88468,11 @@
       <c r="G200">
         <v>820</v>
       </c>
-    </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H200">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="201" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A201">
         <v>2005</v>
       </c>
@@ -87891,8 +88494,11 @@
       <c r="G201">
         <v>800</v>
       </c>
-    </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H201">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A202">
         <v>2005</v>
       </c>
@@ -87914,8 +88520,11 @@
       <c r="G202">
         <v>700</v>
       </c>
-    </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H202">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A203">
         <v>2005</v>
       </c>
@@ -87937,8 +88546,11 @@
       <c r="G203">
         <v>760</v>
       </c>
-    </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H203">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="204" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A204">
         <v>2005</v>
       </c>
@@ -87960,8 +88572,11 @@
       <c r="G204">
         <v>800</v>
       </c>
-    </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H204">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="205" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A205">
         <v>2005</v>
       </c>
@@ -87983,8 +88598,11 @@
       <c r="G205">
         <v>580</v>
       </c>
-    </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H205">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="206" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A206">
         <v>2005</v>
       </c>
@@ -88006,8 +88624,11 @@
       <c r="G206">
         <v>520</v>
       </c>
-    </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H206">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="207" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A207">
         <v>2005</v>
       </c>
@@ -88029,8 +88650,11 @@
       <c r="G207">
         <v>680</v>
       </c>
-    </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H207">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A208">
         <v>2005</v>
       </c>
@@ -88052,8 +88676,11 @@
       <c r="G208">
         <v>700</v>
       </c>
-    </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H208">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="209" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A209">
         <v>2005</v>
       </c>
@@ -88075,8 +88702,11 @@
       <c r="G209">
         <v>800</v>
       </c>
-    </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H209">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="210" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A210">
         <v>2005</v>
       </c>
@@ -88098,8 +88728,11 @@
       <c r="G210">
         <v>740</v>
       </c>
-    </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H210">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="211" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A211">
         <v>2005</v>
       </c>
@@ -88121,8 +88754,11 @@
       <c r="G211">
         <v>770</v>
       </c>
-    </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H211">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="212" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A212">
         <v>2005</v>
       </c>
@@ -88144,8 +88780,11 @@
       <c r="G212">
         <v>390</v>
       </c>
-    </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H212">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="213" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A213">
         <v>2005</v>
       </c>
@@ -88167,8 +88806,11 @@
       <c r="G213">
         <v>480</v>
       </c>
-    </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H213">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="214" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A214">
         <v>2005</v>
       </c>
@@ -88190,8 +88832,11 @@
       <c r="G214">
         <v>600</v>
       </c>
-    </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H214">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="215" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A215">
         <v>2005</v>
       </c>
@@ -88213,8 +88858,11 @@
       <c r="G215">
         <v>520</v>
       </c>
-    </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H215">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="216" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A216">
         <v>2005</v>
       </c>
@@ -88236,8 +88884,11 @@
       <c r="G216">
         <v>520</v>
       </c>
-    </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H216">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="217" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A217">
         <v>2005</v>
       </c>
@@ -88259,8 +88910,11 @@
       <c r="G217">
         <v>790</v>
       </c>
-    </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H217">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="218" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A218">
         <v>2005</v>
       </c>
@@ -88282,8 +88936,11 @@
       <c r="G218">
         <v>790</v>
       </c>
-    </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H218">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="219" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A219">
         <v>2005</v>
       </c>
@@ -88305,8 +88962,11 @@
       <c r="G219">
         <v>810</v>
       </c>
-    </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H219">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="220" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A220">
         <v>2005</v>
       </c>
@@ -88328,8 +88988,11 @@
       <c r="G220">
         <v>820</v>
       </c>
-    </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H220">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="221" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A221">
         <v>2005</v>
       </c>
@@ -88351,8 +89014,11 @@
       <c r="G221">
         <v>800</v>
       </c>
-    </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H221">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="222" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A222">
         <v>2005</v>
       </c>
@@ -88374,8 +89040,11 @@
       <c r="G222">
         <v>700</v>
       </c>
-    </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H222">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="223" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A223">
         <v>2005</v>
       </c>
@@ -88397,8 +89066,11 @@
       <c r="G223">
         <v>760</v>
       </c>
-    </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H223">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="224" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A224">
         <v>2005</v>
       </c>
@@ -88420,8 +89092,11 @@
       <c r="G224">
         <v>800</v>
       </c>
-    </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H224">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="225" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A225">
         <v>2005</v>
       </c>
@@ -88443,8 +89118,11 @@
       <c r="G225">
         <v>580</v>
       </c>
-    </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H225">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="226" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A226">
         <v>2005</v>
       </c>
@@ -88466,8 +89144,11 @@
       <c r="G226">
         <v>520</v>
       </c>
-    </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H226">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="227" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A227">
         <v>2005</v>
       </c>
@@ -88489,8 +89170,11 @@
       <c r="G227">
         <v>680</v>
       </c>
-    </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H227">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="228" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A228">
         <v>2005</v>
       </c>
@@ -88512,8 +89196,11 @@
       <c r="G228">
         <v>700</v>
       </c>
-    </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H228">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="229" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A229">
         <v>2005</v>
       </c>
@@ -88535,8 +89222,11 @@
       <c r="G229">
         <v>800</v>
       </c>
-    </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H229">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="230" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A230">
         <v>2005</v>
       </c>
@@ -88558,8 +89248,11 @@
       <c r="G230">
         <v>740</v>
       </c>
-    </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H230">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="231" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A231">
         <v>2005</v>
       </c>
@@ -88581,8 +89274,11 @@
       <c r="G231">
         <v>770</v>
       </c>
-    </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H231">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="232" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A232">
         <v>2005</v>
       </c>
@@ -88604,8 +89300,11 @@
       <c r="G232">
         <v>390</v>
       </c>
-    </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H232">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="233" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A233">
         <v>2005</v>
       </c>
@@ -88627,8 +89326,11 @@
       <c r="G233">
         <v>480</v>
       </c>
-    </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H233">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="234" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A234">
         <v>2006</v>
       </c>
@@ -88650,8 +89352,11 @@
       <c r="G234">
         <v>600</v>
       </c>
-    </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H234">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="235" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A235">
         <v>2006</v>
       </c>
@@ -88673,8 +89378,11 @@
       <c r="G235">
         <v>520</v>
       </c>
-    </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H235">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="236" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A236">
         <v>2006</v>
       </c>
@@ -88696,8 +89404,11 @@
       <c r="G236">
         <v>520</v>
       </c>
-    </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H236">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="237" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A237">
         <v>2006</v>
       </c>
@@ -88719,8 +89430,11 @@
       <c r="G237">
         <v>790</v>
       </c>
-    </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H237">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="238" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A238">
         <v>2006</v>
       </c>
@@ -88742,8 +89456,11 @@
       <c r="G238">
         <v>790</v>
       </c>
-    </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H238">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="239" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A239">
         <v>2006</v>
       </c>
@@ -88765,8 +89482,11 @@
       <c r="G239">
         <v>810</v>
       </c>
-    </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H239">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="240" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A240">
         <v>2006</v>
       </c>
@@ -88788,8 +89508,11 @@
       <c r="G240">
         <v>820</v>
       </c>
-    </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H240">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="241" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A241">
         <v>2006</v>
       </c>
@@ -88811,8 +89534,11 @@
       <c r="G241">
         <v>800</v>
       </c>
-    </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H241">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="242" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A242">
         <v>2006</v>
       </c>
@@ -88834,8 +89560,11 @@
       <c r="G242">
         <v>700</v>
       </c>
-    </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H242">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="243" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A243">
         <v>2006</v>
       </c>
@@ -88857,8 +89586,11 @@
       <c r="G243">
         <v>760</v>
       </c>
-    </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H243">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="244" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A244">
         <v>2006</v>
       </c>
@@ -88880,8 +89612,11 @@
       <c r="G244">
         <v>800</v>
       </c>
-    </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H244">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="245" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A245">
         <v>2006</v>
       </c>
@@ -88903,8 +89638,11 @@
       <c r="G245">
         <v>580</v>
       </c>
-    </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H245">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="246" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A246">
         <v>2006</v>
       </c>
@@ -88926,8 +89664,11 @@
       <c r="G246">
         <v>520</v>
       </c>
-    </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H246">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="247" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A247">
         <v>2006</v>
       </c>
@@ -88949,8 +89690,11 @@
       <c r="G247">
         <v>680</v>
       </c>
-    </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H247">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="248" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A248">
         <v>2006</v>
       </c>
@@ -88972,8 +89716,11 @@
       <c r="G248">
         <v>700</v>
       </c>
-    </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H248">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="249" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A249">
         <v>2006</v>
       </c>
@@ -88995,8 +89742,11 @@
       <c r="G249">
         <v>800</v>
       </c>
-    </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H249">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="250" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A250">
         <v>2006</v>
       </c>
@@ -89018,8 +89768,11 @@
       <c r="G250">
         <v>740</v>
       </c>
-    </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H250">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="251" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A251">
         <v>2006</v>
       </c>
@@ -89041,8 +89794,11 @@
       <c r="G251">
         <v>390</v>
       </c>
-    </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H251">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="252" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A252">
         <v>2006</v>
       </c>
@@ -89064,8 +89820,11 @@
       <c r="G252">
         <v>480</v>
       </c>
-    </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H252">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="253" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A253">
         <v>2006</v>
       </c>
@@ -89087,8 +89846,11 @@
       <c r="G253">
         <v>600</v>
       </c>
-    </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H253">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="254" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A254">
         <v>2006</v>
       </c>
@@ -89110,8 +89872,11 @@
       <c r="G254">
         <v>520</v>
       </c>
-    </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H254">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="255" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A255">
         <v>2006</v>
       </c>
@@ -89133,8 +89898,11 @@
       <c r="G255">
         <v>520</v>
       </c>
-    </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H255">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="256" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A256">
         <v>2006</v>
       </c>
@@ -89156,8 +89924,11 @@
       <c r="G256">
         <v>790</v>
       </c>
-    </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H256">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="257" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A257">
         <v>2006</v>
       </c>
@@ -89179,8 +89950,11 @@
       <c r="G257">
         <v>790</v>
       </c>
-    </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H257">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="258" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A258">
         <v>2006</v>
       </c>
@@ -89202,8 +89976,11 @@
       <c r="G258">
         <v>810</v>
       </c>
-    </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H258">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="259" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A259">
         <v>2006</v>
       </c>
@@ -89225,8 +90002,11 @@
       <c r="G259">
         <v>800</v>
       </c>
-    </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H259">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="260" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A260">
         <v>2006</v>
       </c>
@@ -89248,8 +90028,11 @@
       <c r="G260">
         <v>700</v>
       </c>
-    </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H260">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="261" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A261">
         <v>2006</v>
       </c>
@@ -89271,8 +90054,11 @@
       <c r="G261">
         <v>760</v>
       </c>
-    </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H261">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="262" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A262">
         <v>2006</v>
       </c>
@@ -89294,8 +90080,11 @@
       <c r="G262">
         <v>800</v>
       </c>
-    </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H262">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="263" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A263">
         <v>2006</v>
       </c>
@@ -89317,8 +90106,11 @@
       <c r="G263">
         <v>580</v>
       </c>
-    </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H263">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="264" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A264">
         <v>2006</v>
       </c>
@@ -89340,8 +90132,11 @@
       <c r="G264">
         <v>520</v>
       </c>
-    </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H264">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="265" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A265">
         <v>2006</v>
       </c>
@@ -89363,8 +90158,11 @@
       <c r="G265">
         <v>680</v>
       </c>
-    </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H265">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="266" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A266">
         <v>2006</v>
       </c>
@@ -89386,8 +90184,11 @@
       <c r="G266">
         <v>700</v>
       </c>
-    </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H266">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="267" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A267">
         <v>2006</v>
       </c>
@@ -89409,8 +90210,11 @@
       <c r="G267">
         <v>800</v>
       </c>
-    </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H267">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="268" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A268">
         <v>2006</v>
       </c>
@@ -89432,8 +90236,11 @@
       <c r="G268">
         <v>740</v>
       </c>
-    </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H268">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="269" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A269">
         <v>2006</v>
       </c>
@@ -89455,8 +90262,11 @@
       <c r="G269">
         <v>770</v>
       </c>
-    </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H269">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="270" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A270">
         <v>2006</v>
       </c>
@@ -89478,8 +90288,11 @@
       <c r="G270">
         <v>390</v>
       </c>
-    </row>
-    <row r="271" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H270">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="271" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A271">
         <v>2006</v>
       </c>
@@ -89501,8 +90314,11 @@
       <c r="G271">
         <v>480</v>
       </c>
-    </row>
-    <row r="272" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H271">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="272" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A272">
         <v>2006</v>
       </c>
@@ -89524,8 +90340,11 @@
       <c r="G272">
         <v>600</v>
       </c>
-    </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H272">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="273" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A273">
         <v>2006</v>
       </c>
@@ -89547,8 +90366,11 @@
       <c r="G273">
         <v>520</v>
       </c>
-    </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H273">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="274" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A274">
         <v>2006</v>
       </c>
@@ -89570,8 +90392,11 @@
       <c r="G274">
         <v>520</v>
       </c>
-    </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H274">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="275" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A275">
         <v>2006</v>
       </c>
@@ -89593,8 +90418,11 @@
       <c r="G275">
         <v>790</v>
       </c>
-    </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H275">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="276" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A276">
         <v>2006</v>
       </c>
@@ -89616,8 +90444,11 @@
       <c r="G276">
         <v>790</v>
       </c>
-    </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H276">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="277" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A277">
         <v>2006</v>
       </c>
@@ -89639,8 +90470,11 @@
       <c r="G277">
         <v>800</v>
       </c>
-    </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H277">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="278" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A278">
         <v>2006</v>
       </c>
@@ -89662,8 +90496,11 @@
       <c r="G278">
         <v>700</v>
       </c>
-    </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H278">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="279" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A279">
         <v>2006</v>
       </c>
@@ -89685,8 +90522,11 @@
       <c r="G279">
         <v>760</v>
       </c>
-    </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H279">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="280" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A280">
         <v>2006</v>
       </c>
@@ -89708,8 +90548,11 @@
       <c r="G280">
         <v>800</v>
       </c>
-    </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H280">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="281" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A281">
         <v>2006</v>
       </c>
@@ -89731,8 +90574,11 @@
       <c r="G281">
         <v>580</v>
       </c>
-    </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H281">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="282" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A282">
         <v>2006</v>
       </c>
@@ -89754,8 +90600,11 @@
       <c r="G282">
         <v>520</v>
       </c>
-    </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H282">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="283" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A283">
         <v>2006</v>
       </c>
@@ -89777,8 +90626,11 @@
       <c r="G283">
         <v>680</v>
       </c>
-    </row>
-    <row r="284" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H283">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="284" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A284">
         <v>2006</v>
       </c>
@@ -89800,8 +90652,11 @@
       <c r="G284">
         <v>700</v>
       </c>
-    </row>
-    <row r="285" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H284">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="285" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A285">
         <v>2006</v>
       </c>
@@ -89823,8 +90678,11 @@
       <c r="G285">
         <v>800</v>
       </c>
-    </row>
-    <row r="286" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H285">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="286" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A286">
         <v>2006</v>
       </c>
@@ -89846,8 +90704,11 @@
       <c r="G286">
         <v>740</v>
       </c>
-    </row>
-    <row r="287" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H286">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="287" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A287">
         <v>2006</v>
       </c>
@@ -89869,8 +90730,11 @@
       <c r="G287">
         <v>770</v>
       </c>
-    </row>
-    <row r="288" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H287">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="288" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A288">
         <v>2006</v>
       </c>
@@ -89892,8 +90756,11 @@
       <c r="G288">
         <v>390</v>
       </c>
-    </row>
-    <row r="289" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H288">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="289" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A289">
         <v>2006</v>
       </c>
@@ -89915,8 +90782,11 @@
       <c r="G289">
         <v>480</v>
       </c>
-    </row>
-    <row r="290" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H289">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="290" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A290">
         <v>2006</v>
       </c>
@@ -89938,8 +90808,11 @@
       <c r="G290">
         <v>600</v>
       </c>
-    </row>
-    <row r="291" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H290">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="291" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A291">
         <v>2006</v>
       </c>
@@ -89961,8 +90834,11 @@
       <c r="G291">
         <v>520</v>
       </c>
-    </row>
-    <row r="292" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H291">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="292" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A292">
         <v>2006</v>
       </c>
@@ -89984,8 +90860,11 @@
       <c r="G292">
         <v>790</v>
       </c>
-    </row>
-    <row r="293" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H292">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="293" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A293">
         <v>2006</v>
       </c>
@@ -90007,8 +90886,11 @@
       <c r="G293">
         <v>790</v>
       </c>
-    </row>
-    <row r="294" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H293">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="294" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A294">
         <v>2006</v>
       </c>
@@ -90030,8 +90912,11 @@
       <c r="G294">
         <v>810</v>
       </c>
-    </row>
-    <row r="295" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H294">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="295" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A295">
         <v>2006</v>
       </c>
@@ -90053,8 +90938,11 @@
       <c r="G295">
         <v>800</v>
       </c>
-    </row>
-    <row r="296" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H295">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="296" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A296">
         <v>2006</v>
       </c>
@@ -90076,8 +90964,11 @@
       <c r="G296">
         <v>760</v>
       </c>
-    </row>
-    <row r="297" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H296">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="297" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A297">
         <v>2006</v>
       </c>
@@ -90099,8 +90990,11 @@
       <c r="G297">
         <v>800</v>
       </c>
-    </row>
-    <row r="298" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H297">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="298" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A298">
         <v>2006</v>
       </c>
@@ -90122,8 +91016,11 @@
       <c r="G298">
         <v>580</v>
       </c>
-    </row>
-    <row r="299" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H298">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="299" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A299">
         <v>2006</v>
       </c>
@@ -90145,8 +91042,11 @@
       <c r="G299">
         <v>580</v>
       </c>
-    </row>
-    <row r="300" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H299">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="300" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A300">
         <v>2006</v>
       </c>
@@ -90168,8 +91068,11 @@
       <c r="G300">
         <v>520</v>
       </c>
-    </row>
-    <row r="301" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H300">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="301" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A301">
         <v>2006</v>
       </c>
@@ -90191,8 +91094,11 @@
       <c r="G301">
         <v>680</v>
       </c>
-    </row>
-    <row r="302" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H301">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="302" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A302">
         <v>2006</v>
       </c>
@@ -90214,8 +91120,11 @@
       <c r="G302">
         <v>700</v>
       </c>
-    </row>
-    <row r="303" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H302">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="303" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A303">
         <v>2006</v>
       </c>
@@ -90237,8 +91146,11 @@
       <c r="G303">
         <v>800</v>
       </c>
-    </row>
-    <row r="304" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H303">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="304" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A304">
         <v>2006</v>
       </c>
@@ -90260,8 +91172,11 @@
       <c r="G304">
         <v>740</v>
       </c>
-    </row>
-    <row r="305" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H304">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="305" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A305">
         <v>2006</v>
       </c>
@@ -90283,8 +91198,11 @@
       <c r="G305">
         <v>390</v>
       </c>
-    </row>
-    <row r="306" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H305">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="306" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A306">
         <v>2006</v>
       </c>
@@ -90305,6 +91223,9 @@
       </c>
       <c r="G306">
         <v>480</v>
+      </c>
+      <c r="H306">
+        <v>305</v>
       </c>
     </row>
   </sheetData>
@@ -90314,1537 +91235,2455 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA6E73EA-7E5A-483F-A3F8-044ADA60D0C8}">
-  <dimension ref="A1:A306"/>
+  <dimension ref="A1:B306"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B1" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>600</v>
       </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>520</v>
       </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>520</v>
       </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>790</v>
       </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>790</v>
       </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>810</v>
       </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>820</v>
       </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>800</v>
       </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>700</v>
       </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B10">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>760</v>
       </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>800</v>
       </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>580</v>
       </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>520</v>
       </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B14">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>680</v>
       </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B15">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>700</v>
       </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B16">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>800</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B17">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>740</v>
       </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B18">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>770</v>
       </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B19">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>600</v>
       </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B20">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>520</v>
       </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B21">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>520</v>
       </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B22">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>790</v>
       </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B23">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>790</v>
       </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B24">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>810</v>
       </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>820</v>
       </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B26">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>800</v>
       </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B27">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>700</v>
       </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B28">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>760</v>
       </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B29">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>800</v>
       </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B30">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>580</v>
       </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B31">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>520</v>
       </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B32">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>680</v>
       </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B33">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>700</v>
       </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B34">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>800</v>
       </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B35">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>740</v>
       </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B36">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>770</v>
       </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B37">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>600</v>
       </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B38">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>520</v>
       </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B39">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>520</v>
       </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B40">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>790</v>
       </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B41">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>790</v>
       </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B42">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>810</v>
       </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B43">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>820</v>
       </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B44">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>800</v>
       </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B45">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>700</v>
       </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B46">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>760</v>
       </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B47">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>800</v>
       </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B48">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>580</v>
       </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B49">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>520</v>
       </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B50">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>680</v>
       </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B51">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>700</v>
       </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B52">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>800</v>
       </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B53">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>740</v>
       </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B54">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>770</v>
       </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B55">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>600</v>
       </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B56">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>520</v>
       </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B57">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>520</v>
       </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B58">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>790</v>
       </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B59">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>790</v>
       </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B60">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>810</v>
       </c>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B61">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>820</v>
       </c>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B62">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>800</v>
       </c>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B63">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>700</v>
       </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B64">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>760</v>
       </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B65">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>800</v>
       </c>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B66">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>580</v>
       </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B67">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>520</v>
       </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B68">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>680</v>
       </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B69">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>700</v>
       </c>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B70">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>800</v>
       </c>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B71">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>740</v>
       </c>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B72">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>770</v>
       </c>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B73">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>600</v>
       </c>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B74">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>520</v>
       </c>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B75">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>520</v>
       </c>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B76">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>790</v>
       </c>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B77">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>790</v>
       </c>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B78">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>810</v>
       </c>
-    </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B79">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>820</v>
       </c>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B80">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>800</v>
       </c>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B81">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>700</v>
       </c>
-    </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B82">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>760</v>
       </c>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B83">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>800</v>
       </c>
-    </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B84">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>580</v>
       </c>
-    </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B85">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>520</v>
       </c>
-    </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B86">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>680</v>
       </c>
-    </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B87">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>700</v>
       </c>
-    </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B88">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>800</v>
       </c>
-    </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B89">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>740</v>
       </c>
-    </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B90">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>770</v>
       </c>
-    </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B91">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>390</v>
       </c>
-    </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B92">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>480</v>
       </c>
-    </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B93">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>600</v>
       </c>
-    </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B94">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>520</v>
       </c>
-    </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B95">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>520</v>
       </c>
-    </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B96">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>790</v>
       </c>
-    </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B97">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>790</v>
       </c>
-    </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B98">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>810</v>
       </c>
-    </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B99">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>820</v>
       </c>
-    </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B100">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>800</v>
       </c>
-    </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B101">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>700</v>
       </c>
-    </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B102">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>760</v>
       </c>
-    </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B103">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>800</v>
       </c>
-    </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B104">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>580</v>
       </c>
-    </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B105">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>520</v>
       </c>
-    </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B106">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>680</v>
       </c>
-    </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B107">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>700</v>
       </c>
-    </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B108">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>800</v>
       </c>
-    </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B109">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>740</v>
       </c>
-    </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B110">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>770</v>
       </c>
-    </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B111">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>390</v>
       </c>
-    </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B112">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>480</v>
       </c>
-    </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B113">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>600</v>
       </c>
-    </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B114">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>520</v>
       </c>
-    </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B115">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>520</v>
       </c>
-    </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B116">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>790</v>
       </c>
-    </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B117">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>790</v>
       </c>
-    </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B118">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>810</v>
       </c>
-    </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B119">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>820</v>
       </c>
-    </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B120">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>800</v>
       </c>
-    </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B121">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>700</v>
       </c>
-    </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B122">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>760</v>
       </c>
-    </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B123">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>800</v>
       </c>
-    </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B124">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>580</v>
       </c>
-    </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B125">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>520</v>
       </c>
-    </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B126">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>680</v>
       </c>
-    </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B127">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>700</v>
       </c>
-    </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B128">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A129">
         <v>800</v>
       </c>
-    </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B129">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>740</v>
       </c>
-    </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B130">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A131">
         <v>770</v>
       </c>
-    </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B131">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>390</v>
       </c>
-    </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B132">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>480</v>
       </c>
-    </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B133">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>600</v>
       </c>
-    </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B134">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>520</v>
       </c>
-    </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B135">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>520</v>
       </c>
-    </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B136">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A137">
         <v>790</v>
       </c>
-    </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B137">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>790</v>
       </c>
-    </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B138">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>810</v>
       </c>
-    </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B139">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>820</v>
       </c>
-    </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B140">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A141">
         <v>800</v>
       </c>
-    </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B141">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A142">
         <v>700</v>
       </c>
-    </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B142">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A143">
         <v>760</v>
       </c>
-    </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B143">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A144">
         <v>800</v>
       </c>
-    </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B144">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A145">
         <v>580</v>
       </c>
-    </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B145">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>520</v>
       </c>
-    </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B146">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A147">
         <v>680</v>
       </c>
-    </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B147">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>700</v>
       </c>
-    </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B148">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>800</v>
       </c>
-    </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B149">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>740</v>
       </c>
-    </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B150">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A151">
         <v>770</v>
       </c>
-    </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B151">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>390</v>
       </c>
-    </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B152">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A153">
         <v>480</v>
       </c>
-    </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B153">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A154">
         <v>600</v>
       </c>
-    </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B154">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A155">
         <v>520</v>
       </c>
-    </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B155">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A156">
         <v>520</v>
       </c>
-    </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B156">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A157">
         <v>790</v>
       </c>
-    </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B157">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A158">
         <v>790</v>
       </c>
-    </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B158">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A159">
         <v>810</v>
       </c>
-    </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B159">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A160">
         <v>820</v>
       </c>
-    </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B160">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A161">
         <v>800</v>
       </c>
-    </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B161">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A162">
         <v>700</v>
       </c>
-    </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B162">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A163">
         <v>760</v>
       </c>
-    </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B163">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A164">
         <v>800</v>
       </c>
-    </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B164">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A165">
         <v>580</v>
       </c>
-    </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B165">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A166">
         <v>520</v>
       </c>
-    </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B166">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A167">
         <v>680</v>
       </c>
-    </row>
-    <row r="168" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B167">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A168">
         <v>700</v>
       </c>
-    </row>
-    <row r="169" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B168">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A169">
         <v>800</v>
       </c>
-    </row>
-    <row r="170" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B169">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A170">
         <v>740</v>
       </c>
-    </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B170">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A171">
         <v>770</v>
       </c>
-    </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B171">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A172">
         <v>390</v>
       </c>
-    </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B172">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A173">
         <v>480</v>
       </c>
-    </row>
-    <row r="174" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B173">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A174">
         <v>600</v>
       </c>
-    </row>
-    <row r="175" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B174">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A175">
         <v>520</v>
       </c>
-    </row>
-    <row r="176" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B175">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A176">
         <v>520</v>
       </c>
-    </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B176">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A177">
         <v>790</v>
       </c>
-    </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B177">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A178">
         <v>790</v>
       </c>
-    </row>
-    <row r="179" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B178">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A179">
         <v>810</v>
       </c>
-    </row>
-    <row r="180" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B179">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A180">
         <v>820</v>
       </c>
-    </row>
-    <row r="181" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B180">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A181">
         <v>800</v>
       </c>
-    </row>
-    <row r="182" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B181">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A182">
         <v>700</v>
       </c>
-    </row>
-    <row r="183" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B182">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A183">
         <v>760</v>
       </c>
-    </row>
-    <row r="184" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B183">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A184">
         <v>800</v>
       </c>
-    </row>
-    <row r="185" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B184">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A185">
         <v>580</v>
       </c>
-    </row>
-    <row r="186" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B185">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A186">
         <v>520</v>
       </c>
-    </row>
-    <row r="187" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B186">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A187">
         <v>680</v>
       </c>
-    </row>
-    <row r="188" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B187">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A188">
         <v>700</v>
       </c>
-    </row>
-    <row r="189" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B188">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A189">
         <v>800</v>
       </c>
-    </row>
-    <row r="190" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B189">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A190">
         <v>740</v>
       </c>
-    </row>
-    <row r="191" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B190">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A191">
         <v>770</v>
       </c>
-    </row>
-    <row r="192" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B191">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A192">
         <v>390</v>
       </c>
-    </row>
-    <row r="193" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B192">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A193">
         <v>480</v>
       </c>
-    </row>
-    <row r="194" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B193">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A194">
         <v>600</v>
       </c>
-    </row>
-    <row r="195" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B194">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A195">
         <v>520</v>
       </c>
-    </row>
-    <row r="196" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B195">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A196">
         <v>520</v>
       </c>
-    </row>
-    <row r="197" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B196">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A197">
         <v>790</v>
       </c>
-    </row>
-    <row r="198" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B197">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A198">
         <v>790</v>
       </c>
-    </row>
-    <row r="199" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B198">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A199">
         <v>810</v>
       </c>
-    </row>
-    <row r="200" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B199">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A200">
         <v>820</v>
       </c>
-    </row>
-    <row r="201" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B200">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A201">
         <v>800</v>
       </c>
-    </row>
-    <row r="202" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B201">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A202">
         <v>700</v>
       </c>
-    </row>
-    <row r="203" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B202">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A203">
         <v>760</v>
       </c>
-    </row>
-    <row r="204" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B203">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A204">
         <v>800</v>
       </c>
-    </row>
-    <row r="205" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B204">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A205">
         <v>580</v>
       </c>
-    </row>
-    <row r="206" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B205">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A206">
         <v>520</v>
       </c>
-    </row>
-    <row r="207" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B206">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A207">
         <v>680</v>
       </c>
-    </row>
-    <row r="208" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B207">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A208">
         <v>700</v>
       </c>
-    </row>
-    <row r="209" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B208">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A209">
         <v>800</v>
       </c>
-    </row>
-    <row r="210" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B209">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A210">
         <v>740</v>
       </c>
-    </row>
-    <row r="211" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B210">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A211">
         <v>770</v>
       </c>
-    </row>
-    <row r="212" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B211">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A212">
         <v>390</v>
       </c>
-    </row>
-    <row r="213" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B212">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A213">
         <v>480</v>
       </c>
-    </row>
-    <row r="214" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B213">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A214">
         <v>600</v>
       </c>
-    </row>
-    <row r="215" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B214">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A215">
         <v>520</v>
       </c>
-    </row>
-    <row r="216" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B215">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A216">
         <v>520</v>
       </c>
-    </row>
-    <row r="217" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B216">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A217">
         <v>790</v>
       </c>
-    </row>
-    <row r="218" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B217">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A218">
         <v>790</v>
       </c>
-    </row>
-    <row r="219" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B218">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A219">
         <v>810</v>
       </c>
-    </row>
-    <row r="220" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B219">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A220">
         <v>820</v>
       </c>
-    </row>
-    <row r="221" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B220">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A221">
         <v>800</v>
       </c>
-    </row>
-    <row r="222" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B221">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A222">
         <v>700</v>
       </c>
-    </row>
-    <row r="223" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B222">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A223">
         <v>760</v>
       </c>
-    </row>
-    <row r="224" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B223">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A224">
         <v>800</v>
       </c>
-    </row>
-    <row r="225" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B224">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A225">
         <v>580</v>
       </c>
-    </row>
-    <row r="226" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B225">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A226">
         <v>520</v>
       </c>
-    </row>
-    <row r="227" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B226">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A227">
         <v>680</v>
       </c>
-    </row>
-    <row r="228" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B227">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A228">
         <v>700</v>
       </c>
-    </row>
-    <row r="229" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B228">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A229">
         <v>800</v>
       </c>
-    </row>
-    <row r="230" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B229">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A230">
         <v>740</v>
       </c>
-    </row>
-    <row r="231" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B230">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A231">
         <v>770</v>
       </c>
-    </row>
-    <row r="232" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B231">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A232">
         <v>390</v>
       </c>
-    </row>
-    <row r="233" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B232">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A233">
         <v>480</v>
       </c>
-    </row>
-    <row r="234" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B233">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A234">
         <v>600</v>
       </c>
-    </row>
-    <row r="235" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B234">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A235">
         <v>520</v>
       </c>
-    </row>
-    <row r="236" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B235">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A236">
         <v>520</v>
       </c>
-    </row>
-    <row r="237" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B236">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A237">
         <v>790</v>
       </c>
-    </row>
-    <row r="238" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B237">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A238">
         <v>790</v>
       </c>
-    </row>
-    <row r="239" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B238">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A239">
         <v>810</v>
       </c>
-    </row>
-    <row r="240" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B239">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A240">
         <v>820</v>
       </c>
-    </row>
-    <row r="241" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B240">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A241">
         <v>800</v>
       </c>
-    </row>
-    <row r="242" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B241">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A242">
         <v>700</v>
       </c>
-    </row>
-    <row r="243" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B242">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A243">
         <v>760</v>
       </c>
-    </row>
-    <row r="244" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B243">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A244">
         <v>800</v>
       </c>
-    </row>
-    <row r="245" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B244">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A245">
         <v>580</v>
       </c>
-    </row>
-    <row r="246" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B245">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A246">
         <v>520</v>
       </c>
-    </row>
-    <row r="247" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B246">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A247">
         <v>680</v>
       </c>
-    </row>
-    <row r="248" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B247">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A248">
         <v>700</v>
       </c>
-    </row>
-    <row r="249" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B248">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A249">
         <v>800</v>
       </c>
-    </row>
-    <row r="250" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B249">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A250">
         <v>740</v>
       </c>
-    </row>
-    <row r="251" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B250">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A251">
         <v>390</v>
       </c>
-    </row>
-    <row r="252" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B251">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A252">
         <v>480</v>
       </c>
-    </row>
-    <row r="253" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B252">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A253">
         <v>600</v>
       </c>
-    </row>
-    <row r="254" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B253">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A254">
         <v>520</v>
       </c>
-    </row>
-    <row r="255" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B254">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A255">
         <v>520</v>
       </c>
-    </row>
-    <row r="256" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B255">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A256">
         <v>790</v>
       </c>
-    </row>
-    <row r="257" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B256">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A257">
         <v>790</v>
       </c>
-    </row>
-    <row r="258" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B257">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A258">
         <v>810</v>
       </c>
-    </row>
-    <row r="259" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B258">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A259">
         <v>800</v>
       </c>
-    </row>
-    <row r="260" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B259">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A260">
         <v>700</v>
       </c>
-    </row>
-    <row r="261" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B260">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A261">
         <v>760</v>
       </c>
-    </row>
-    <row r="262" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B261">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A262">
         <v>800</v>
       </c>
-    </row>
-    <row r="263" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B262">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A263">
         <v>580</v>
       </c>
-    </row>
-    <row r="264" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B263">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A264">
         <v>520</v>
       </c>
-    </row>
-    <row r="265" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B264">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A265">
         <v>680</v>
       </c>
-    </row>
-    <row r="266" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B265">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A266">
         <v>700</v>
       </c>
-    </row>
-    <row r="267" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B266">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A267">
         <v>800</v>
       </c>
-    </row>
-    <row r="268" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B267">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A268">
         <v>740</v>
       </c>
-    </row>
-    <row r="269" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B268">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A269">
         <v>770</v>
       </c>
-    </row>
-    <row r="270" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B269">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A270">
         <v>390</v>
       </c>
-    </row>
-    <row r="271" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B270">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A271">
         <v>480</v>
       </c>
-    </row>
-    <row r="272" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B271">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A272">
         <v>600</v>
       </c>
-    </row>
-    <row r="273" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B272">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A273">
         <v>520</v>
       </c>
-    </row>
-    <row r="274" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B273">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A274">
         <v>520</v>
       </c>
-    </row>
-    <row r="275" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B274">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A275">
         <v>790</v>
       </c>
-    </row>
-    <row r="276" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B275">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A276">
         <v>790</v>
       </c>
-    </row>
-    <row r="277" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B276">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A277">
         <v>800</v>
       </c>
-    </row>
-    <row r="278" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B277">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A278">
         <v>700</v>
       </c>
-    </row>
-    <row r="279" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B278">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A279">
         <v>760</v>
       </c>
-    </row>
-    <row r="280" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B279">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A280">
         <v>800</v>
       </c>
-    </row>
-    <row r="281" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B280">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A281">
         <v>580</v>
       </c>
-    </row>
-    <row r="282" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B281">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="282" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A282">
         <v>520</v>
       </c>
-    </row>
-    <row r="283" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B282">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A283">
         <v>680</v>
       </c>
-    </row>
-    <row r="284" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B283">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A284">
         <v>700</v>
       </c>
-    </row>
-    <row r="285" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B284">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A285">
         <v>800</v>
       </c>
-    </row>
-    <row r="286" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B285">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A286">
         <v>740</v>
       </c>
-    </row>
-    <row r="287" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B286">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A287">
         <v>770</v>
       </c>
-    </row>
-    <row r="288" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B287">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A288">
         <v>390</v>
       </c>
-    </row>
-    <row r="289" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B288">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="289" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A289">
         <v>480</v>
       </c>
-    </row>
-    <row r="290" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B289">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A290">
         <v>600</v>
       </c>
-    </row>
-    <row r="291" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B290">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="291" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A291">
         <v>520</v>
       </c>
-    </row>
-    <row r="292" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B291">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="292" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A292">
         <v>790</v>
       </c>
-    </row>
-    <row r="293" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B292">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A293">
         <v>790</v>
       </c>
-    </row>
-    <row r="294" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B293">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A294">
         <v>810</v>
       </c>
-    </row>
-    <row r="295" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B294">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A295">
         <v>800</v>
       </c>
-    </row>
-    <row r="296" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B295">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="296" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A296">
         <v>760</v>
       </c>
-    </row>
-    <row r="297" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B296">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="297" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A297">
         <v>800</v>
       </c>
-    </row>
-    <row r="298" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B297">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A298">
         <v>580</v>
       </c>
-    </row>
-    <row r="299" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B298">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A299">
         <v>580</v>
       </c>
-    </row>
-    <row r="300" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B299">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="300" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A300">
         <v>520</v>
       </c>
-    </row>
-    <row r="301" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B300">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="301" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A301">
         <v>680</v>
       </c>
-    </row>
-    <row r="302" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B301">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="302" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A302">
         <v>700</v>
       </c>
-    </row>
-    <row r="303" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B302">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="303" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A303">
         <v>800</v>
       </c>
-    </row>
-    <row r="304" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B303">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="304" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A304">
         <v>740</v>
       </c>
-    </row>
-    <row r="305" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B304">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="305" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A305">
         <v>390</v>
       </c>
-    </row>
-    <row r="306" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B305">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="306" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A306">
         <v>480</v>
+      </c>
+      <c r="B306">
+        <v>305</v>
       </c>
     </row>
   </sheetData>
